--- a/data/raw/cvir_qpcr24_dermo_runs_std_curve.xlsx
+++ b/data/raw/cvir_qpcr24_dermo_runs_std_curve.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="19">
   <si>
     <t>dilution</t>
   </si>
@@ -65,13 +65,16 @@
   </si>
   <si>
     <t>09.23.26</t>
+  </si>
+  <si>
+    <t>09.30.26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -88,6 +91,11 @@
       <color rgb="FF000000"/>
       <name val="&quot;Times New Roman&quot;"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -103,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -111,6 +119,9 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -815,9 +826,108 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
+      <c r="A45" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" s="2">
+        <v>21.02</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="2">
+        <v>24.97</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="2">
+        <v>28.12</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="2">
+        <v>31.46</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="2">
+        <v>35.43</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="2">
+        <v>38.61</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" s="2">
+        <v>40.81</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="2">
+        <v>44.22</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
